--- a/Excel/ExpConfig.xlsx
+++ b/Excel/ExpConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E273A764-167F-4252-8049-FD3170D39AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC3FD2D5-E28B-46DB-9602-D82B93E650EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -98,6 +98,7 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -111,12 +112,14 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="0"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -124,6 +127,7 @@
       <sz val="10"/>
       <color theme="0"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -131,6 +135,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -138,12 +143,14 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2000,7 +2007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:Q75"/>
+  <dimension ref="C1:Q100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="14" customWidth="1"/>
@@ -2122,7 +2129,7 @@
       <c r="C6" s="8">
         <v>1</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <v>225</v>
       </c>
       <c r="E6" s="8">
@@ -2156,7 +2163,7 @@
       <c r="C7" s="8">
         <v>2</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="8">
         <v>500</v>
       </c>
       <c r="E7" s="8">
@@ -2195,7 +2202,7 @@
       <c r="C8" s="8">
         <v>3</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="8">
         <v>1125</v>
       </c>
       <c r="E8" s="8">
@@ -2234,7 +2241,7 @@
       <c r="C9" s="8">
         <v>4</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="8">
         <v>1350</v>
       </c>
       <c r="E9" s="8">
@@ -2273,7 +2280,7 @@
       <c r="C10" s="8">
         <v>5</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <v>2600</v>
       </c>
       <c r="E10" s="8">
@@ -2312,7 +2319,7 @@
       <c r="C11" s="8">
         <v>6</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="8">
         <v>4250</v>
       </c>
       <c r="E11" s="8">
@@ -2351,7 +2358,7 @@
       <c r="C12" s="8">
         <v>7</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="8">
         <v>6600</v>
       </c>
       <c r="E12" s="8">
@@ -2390,7 +2397,7 @@
       <c r="C13" s="8">
         <v>8</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="8">
         <v>8400</v>
       </c>
       <c r="E13" s="8">
@@ -2429,7 +2436,7 @@
       <c r="C14" s="8">
         <v>9</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="8">
         <v>10000</v>
       </c>
       <c r="E14" s="8">
@@ -2468,7 +2475,7 @@
       <c r="C15" s="8">
         <v>10</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="8">
         <v>12825</v>
       </c>
       <c r="E15" s="8">
@@ -2507,7 +2514,7 @@
       <c r="C16" s="8">
         <v>11</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="8">
         <v>16060</v>
       </c>
       <c r="E16" s="8">
@@ -2546,7 +2553,7 @@
       <c r="C17" s="8">
         <v>12</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="8">
         <v>19500</v>
       </c>
       <c r="E17" s="8">
@@ -2585,7 +2592,7 @@
       <c r="C18" s="8">
         <v>13</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="8">
         <v>22400</v>
       </c>
       <c r="E18" s="8">
@@ -2624,7 +2631,7 @@
       <c r="C19" s="8">
         <v>14</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="8">
         <v>27280</v>
       </c>
       <c r="E19" s="8">
@@ -2663,7 +2670,7 @@
       <c r="C20" s="8">
         <v>15</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="8">
         <v>47420</v>
       </c>
       <c r="E20" s="8">
@@ -2702,7 +2709,7 @@
       <c r="C21" s="8">
         <v>16</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="8">
         <v>54380</v>
       </c>
       <c r="E21" s="8">
@@ -2741,7 +2748,7 @@
       <c r="C22" s="8">
         <v>17</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="8">
         <v>61740</v>
       </c>
       <c r="E22" s="8">
@@ -2780,7 +2787,7 @@
       <c r="C23" s="8">
         <v>18</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="8">
         <v>69500</v>
       </c>
       <c r="E23" s="8">
@@ -2819,7 +2826,7 @@
       <c r="C24" s="8">
         <v>19</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="8">
         <v>110300</v>
       </c>
       <c r="E24" s="8">
@@ -2858,7 +2865,7 @@
       <c r="C25" s="8">
         <v>20</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="8">
         <v>122220</v>
       </c>
       <c r="E25" s="8">
@@ -2897,7 +2904,7 @@
       <c r="C26" s="8">
         <v>21</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="8">
         <v>135050</v>
       </c>
       <c r="E26" s="8">
@@ -2936,7 +2943,7 @@
       <c r="C27" s="8">
         <v>22</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="8">
         <v>148200</v>
       </c>
       <c r="E27" s="8">
@@ -2975,7 +2982,7 @@
       <c r="C28" s="8">
         <v>23</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="8">
         <v>161950</v>
       </c>
       <c r="E28" s="8">
@@ -3014,7 +3021,7 @@
       <c r="C29" s="8">
         <v>24</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="8">
         <v>176300</v>
       </c>
       <c r="E29" s="8">
@@ -3053,7 +3060,7 @@
       <c r="C30" s="8">
         <v>25</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="8">
         <v>191250</v>
       </c>
       <c r="E30" s="8">
@@ -3092,7 +3099,7 @@
       <c r="C31" s="8">
         <v>26</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="8">
         <v>207260</v>
       </c>
       <c r="E31" s="8">
@@ -3131,7 +3138,7 @@
       <c r="C32" s="8">
         <v>27</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="8">
         <v>223440</v>
       </c>
       <c r="E32" s="8">
@@ -3170,7 +3177,7 @@
       <c r="C33" s="8">
         <v>28</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D33" s="8">
         <v>240220</v>
       </c>
       <c r="E33" s="8">
@@ -3209,7 +3216,7 @@
       <c r="C34" s="8">
         <v>29</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="8">
         <v>299800</v>
       </c>
       <c r="E34" s="8">
@@ -3248,7 +3255,7 @@
       <c r="C35" s="8">
         <v>30</v>
       </c>
-      <c r="D35" s="9">
+      <c r="D35" s="8">
         <v>432680</v>
       </c>
       <c r="E35" s="8">
@@ -3287,7 +3294,7 @@
       <c r="C36" s="8">
         <v>31</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="8">
         <v>456520</v>
       </c>
       <c r="E36" s="8">
@@ -3326,7 +3333,7 @@
       <c r="C37" s="8">
         <v>32</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D37" s="8">
         <v>480380</v>
       </c>
       <c r="E37" s="8">
@@ -3365,7 +3372,7 @@
       <c r="C38" s="8">
         <v>33</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="8">
         <v>504840</v>
       </c>
       <c r="E38" s="8">
@@ -3404,7 +3411,7 @@
       <c r="C39" s="8">
         <v>34</v>
       </c>
-      <c r="D39" s="9">
+      <c r="D39" s="8">
         <v>529900</v>
       </c>
       <c r="E39" s="8">
@@ -3443,7 +3450,7 @@
       <c r="C40" s="8">
         <v>35</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="8">
         <v>555560</v>
       </c>
       <c r="E40" s="8">
@@ -3482,7 +3489,7 @@
       <c r="C41" s="8">
         <v>36</v>
       </c>
-      <c r="D41" s="9">
+      <c r="D41" s="8">
         <v>582580</v>
       </c>
       <c r="E41" s="8">
@@ -3521,7 +3528,7 @@
       <c r="C42" s="8">
         <v>37</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="8">
         <v>609470</v>
       </c>
       <c r="E42" s="8">
@@ -3560,7 +3567,7 @@
       <c r="C43" s="8">
         <v>38</v>
       </c>
-      <c r="D43" s="9">
+      <c r="D43" s="8">
         <v>636960</v>
       </c>
       <c r="E43" s="8">
@@ -3599,7 +3606,7 @@
       <c r="C44" s="8">
         <v>39</v>
       </c>
-      <c r="D44" s="9">
+      <c r="D44" s="8">
         <v>738000</v>
       </c>
       <c r="E44" s="8">
@@ -3638,7 +3645,7 @@
       <c r="C45" s="8">
         <v>40</v>
       </c>
-      <c r="D45" s="9">
+      <c r="D45" s="8">
         <v>928840</v>
       </c>
       <c r="E45" s="8">
@@ -3677,7 +3684,7 @@
       <c r="C46" s="8">
         <v>41</v>
       </c>
-      <c r="D46" s="9">
+      <c r="D46" s="8">
         <v>962780</v>
       </c>
       <c r="E46" s="8">
@@ -3716,7 +3723,7 @@
       <c r="C47" s="8">
         <v>42</v>
       </c>
-      <c r="D47" s="9">
+      <c r="D47" s="8">
         <v>997320</v>
       </c>
       <c r="E47" s="8">
@@ -3755,7 +3762,7 @@
       <c r="C48" s="8">
         <v>43</v>
       </c>
-      <c r="D48" s="9">
+      <c r="D48" s="8">
         <v>1032460</v>
       </c>
       <c r="E48" s="8">
@@ -3794,7 +3801,7 @@
       <c r="C49" s="8">
         <v>44</v>
       </c>
-      <c r="D49" s="9">
+      <c r="D49" s="8">
         <v>1068200</v>
       </c>
       <c r="E49" s="8">
@@ -3833,7 +3840,7 @@
       <c r="C50" s="8">
         <v>45</v>
       </c>
-      <c r="D50" s="9">
+      <c r="D50" s="8">
         <v>1104540</v>
       </c>
       <c r="E50" s="8">
@@ -3872,7 +3879,7 @@
       <c r="C51" s="8">
         <v>46</v>
       </c>
-      <c r="D51" s="9">
+      <c r="D51" s="8">
         <v>1141480</v>
       </c>
       <c r="E51" s="8">
@@ -3911,7 +3918,7 @@
       <c r="C52" s="8">
         <v>47</v>
       </c>
-      <c r="D52" s="9">
+      <c r="D52" s="8">
         <v>1179020</v>
       </c>
       <c r="E52" s="8">
@@ -3950,7 +3957,7 @@
       <c r="C53" s="8">
         <v>48</v>
       </c>
-      <c r="D53" s="9">
+      <c r="D53" s="8">
         <v>1217160</v>
       </c>
       <c r="E53" s="8">
@@ -3989,7 +3996,7 @@
       <c r="C54" s="8">
         <v>49</v>
       </c>
-      <c r="D54" s="9">
+      <c r="D54" s="8">
         <v>1463300</v>
       </c>
       <c r="E54" s="8">
@@ -4028,7 +4035,7 @@
       <c r="C55" s="8">
         <v>50</v>
       </c>
-      <c r="D55" s="9">
+      <c r="D55" s="8">
         <v>1826050</v>
       </c>
       <c r="E55" s="8">
@@ -4067,7 +4074,7 @@
       <c r="C56" s="8">
         <v>51</v>
       </c>
-      <c r="D56" s="9">
+      <c r="D56" s="8">
         <v>1971300</v>
       </c>
       <c r="E56" s="8">
@@ -4106,7 +4113,7 @@
       <c r="C57" s="8">
         <v>52</v>
       </c>
-      <c r="D57" s="9">
+      <c r="D57" s="8">
         <v>2243500</v>
       </c>
       <c r="E57" s="8">
@@ -4145,7 +4152,7 @@
       <c r="C58" s="8">
         <v>53</v>
       </c>
-      <c r="D58" s="9">
+      <c r="D58" s="8">
         <v>2521700</v>
       </c>
       <c r="E58" s="8">
@@ -4184,7 +4191,7 @@
       <c r="C59" s="8">
         <v>54</v>
       </c>
-      <c r="D59" s="9">
+      <c r="D59" s="8">
         <v>2805900</v>
       </c>
       <c r="E59" s="8">
@@ -4223,7 +4230,7 @@
       <c r="C60" s="8">
         <v>55</v>
       </c>
-      <c r="D60" s="9">
+      <c r="D60" s="8">
         <v>3096100</v>
       </c>
       <c r="E60" s="8">
@@ -4262,7 +4269,7 @@
       <c r="C61" s="8">
         <v>56</v>
       </c>
-      <c r="D61" s="9">
+      <c r="D61" s="8">
         <v>3392300</v>
       </c>
       <c r="E61" s="8">
@@ -4301,7 +4308,7 @@
       <c r="C62" s="8">
         <v>57</v>
       </c>
-      <c r="D62" s="9">
+      <c r="D62" s="8">
         <v>3694500</v>
       </c>
       <c r="E62" s="8">
@@ -4340,7 +4347,7 @@
       <c r="C63" s="8">
         <v>58</v>
       </c>
-      <c r="D63" s="9">
+      <c r="D63" s="8">
         <v>4268600</v>
       </c>
       <c r="E63" s="8">
@@ -4379,7 +4386,7 @@
       <c r="C64" s="8">
         <v>59</v>
       </c>
-      <c r="D64" s="9">
+      <c r="D64" s="8">
         <v>4854700</v>
       </c>
       <c r="E64" s="8">
@@ -4418,7 +4425,7 @@
       <c r="C65" s="8">
         <v>60</v>
       </c>
-      <c r="D65" s="9">
+      <c r="D65" s="8">
         <v>5452800</v>
       </c>
       <c r="E65" s="8">
@@ -4457,7 +4464,7 @@
       <c r="C66" s="8">
         <v>61</v>
       </c>
-      <c r="D66" s="9">
+      <c r="D66" s="8">
         <v>6887600</v>
       </c>
       <c r="E66" s="8">
@@ -4496,7 +4503,7 @@
       <c r="C67" s="8">
         <v>62</v>
       </c>
-      <c r="D67" s="9">
+      <c r="D67" s="8">
         <v>9186100</v>
       </c>
       <c r="E67" s="8">
@@ -4535,7 +4542,7 @@
       <c r="C68" s="8">
         <v>63</v>
       </c>
-      <c r="D68" s="9">
+      <c r="D68" s="8">
         <v>12094400</v>
       </c>
       <c r="E68" s="8">
@@ -4574,7 +4581,7 @@
       <c r="C69" s="8">
         <v>64</v>
       </c>
-      <c r="D69" s="9">
+      <c r="D69" s="8">
         <v>15630500</v>
       </c>
       <c r="E69" s="8">
@@ -4613,7 +4620,7 @@
       <c r="C70" s="8">
         <v>65</v>
       </c>
-      <c r="D70" s="9">
+      <c r="D70" s="8">
         <v>20099300</v>
       </c>
       <c r="E70" s="8">
@@ -4652,7 +4659,7 @@
       <c r="C71" s="8">
         <v>66</v>
       </c>
-      <c r="D71" s="9">
+      <c r="D71" s="8">
         <v>26091000</v>
       </c>
       <c r="E71" s="8">
@@ -4691,7 +4698,7 @@
       <c r="C72" s="8">
         <v>67</v>
       </c>
-      <c r="D72" s="9">
+      <c r="D72" s="8">
         <v>35148000</v>
       </c>
       <c r="E72" s="8">
@@ -4704,15 +4711,15 @@
         <v>6300</v>
       </c>
       <c r="H72" s="11">
-        <f t="shared" ref="H72:H75" si="8">H71+5</f>
+        <f t="shared" ref="H72:H80" si="8">H71+5</f>
         <v>480</v>
       </c>
       <c r="I72" s="8">
-        <f t="shared" ref="I72:I75" si="9">I71+100</f>
+        <f t="shared" ref="I72:I80" si="9">I71+100</f>
         <v>7600</v>
       </c>
       <c r="J72" s="8">
-        <f t="shared" ref="J72:J75" si="10">J71+20</f>
+        <f t="shared" ref="J72:J80" si="10">J71+20</f>
         <v>1420</v>
       </c>
       <c r="K72" s="8">
@@ -4730,7 +4737,7 @@
       <c r="C73" s="8">
         <v>68</v>
       </c>
-      <c r="D73" s="9">
+      <c r="D73" s="8">
         <v>47344000</v>
       </c>
       <c r="E73" s="8">
@@ -4769,7 +4776,7 @@
       <c r="C74" s="8">
         <v>69</v>
       </c>
-      <c r="D74" s="9">
+      <c r="D74" s="8">
         <v>59780000</v>
       </c>
       <c r="E74" s="8">
@@ -4808,7 +4815,7 @@
       <c r="C75" s="8">
         <v>70</v>
       </c>
-      <c r="D75" s="9">
+      <c r="D75" s="8">
         <v>75475000</v>
       </c>
       <c r="E75" s="8">
@@ -4843,6 +4850,211 @@
       <c r="M75" s="9"/>
       <c r="N75" s="9"/>
     </row>
+    <row r="76" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C76" s="8">
+        <v>71</v>
+      </c>
+      <c r="D76" s="8">
+        <v>91470000</v>
+      </c>
+      <c r="E76" s="8">
+        <v>2600000</v>
+      </c>
+      <c r="F76" s="8">
+        <v>137500</v>
+      </c>
+      <c r="G76" s="11">
+        <v>6800</v>
+      </c>
+      <c r="H76" s="11">
+        <f t="shared" si="8"/>
+        <v>500</v>
+      </c>
+      <c r="I76" s="8">
+        <f t="shared" si="9"/>
+        <v>8000</v>
+      </c>
+      <c r="J76" s="8">
+        <f t="shared" si="10"/>
+        <v>1500</v>
+      </c>
+      <c r="K76" s="8">
+        <f t="shared" ref="K76:L76" si="12">K75+5</f>
+        <v>380</v>
+      </c>
+      <c r="L76" s="8">
+        <f t="shared" si="12"/>
+        <v>380</v>
+      </c>
+    </row>
+    <row r="77" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C77" s="8">
+        <v>72</v>
+      </c>
+      <c r="D77" s="8">
+        <v>107765000</v>
+      </c>
+      <c r="E77" s="8">
+        <v>2700000</v>
+      </c>
+      <c r="F77" s="8">
+        <v>140500</v>
+      </c>
+      <c r="G77" s="11">
+        <v>6925</v>
+      </c>
+      <c r="H77" s="11">
+        <f t="shared" si="8"/>
+        <v>505</v>
+      </c>
+      <c r="I77" s="8">
+        <f t="shared" si="9"/>
+        <v>8100</v>
+      </c>
+      <c r="J77" s="8">
+        <f t="shared" si="10"/>
+        <v>1520</v>
+      </c>
+      <c r="K77" s="8">
+        <f t="shared" ref="K77:L77" si="13">K76+5</f>
+        <v>385</v>
+      </c>
+      <c r="L77" s="8">
+        <f t="shared" si="13"/>
+        <v>385</v>
+      </c>
+    </row>
+    <row r="78" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C78" s="8">
+        <v>73</v>
+      </c>
+      <c r="D78" s="8">
+        <v>124360000</v>
+      </c>
+      <c r="E78" s="8">
+        <v>2800000</v>
+      </c>
+      <c r="F78" s="8">
+        <v>143500</v>
+      </c>
+      <c r="G78" s="11">
+        <v>7050</v>
+      </c>
+      <c r="H78" s="11">
+        <f t="shared" si="8"/>
+        <v>510</v>
+      </c>
+      <c r="I78" s="8">
+        <f t="shared" si="9"/>
+        <v>8200</v>
+      </c>
+      <c r="J78" s="8">
+        <f t="shared" si="10"/>
+        <v>1540</v>
+      </c>
+      <c r="K78" s="8">
+        <f t="shared" ref="K78:L78" si="14">K77+5</f>
+        <v>390</v>
+      </c>
+      <c r="L78" s="8">
+        <f t="shared" si="14"/>
+        <v>390</v>
+      </c>
+    </row>
+    <row r="79" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C79" s="8">
+        <v>74</v>
+      </c>
+      <c r="D79" s="8">
+        <v>156950000</v>
+      </c>
+      <c r="E79" s="8">
+        <v>2900000</v>
+      </c>
+      <c r="F79" s="8">
+        <v>146500</v>
+      </c>
+      <c r="G79" s="11">
+        <v>7175</v>
+      </c>
+      <c r="H79" s="11">
+        <f t="shared" si="8"/>
+        <v>515</v>
+      </c>
+      <c r="I79" s="8">
+        <f t="shared" si="9"/>
+        <v>8300</v>
+      </c>
+      <c r="J79" s="8">
+        <f t="shared" si="10"/>
+        <v>1560</v>
+      </c>
+      <c r="K79" s="8">
+        <f t="shared" ref="K79:L79" si="15">K78+5</f>
+        <v>395</v>
+      </c>
+      <c r="L79" s="8">
+        <f t="shared" si="15"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="80" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C80" s="8">
+        <v>75</v>
+      </c>
+      <c r="D80" s="8">
+        <v>190140000</v>
+      </c>
+      <c r="E80" s="8">
+        <v>3000000</v>
+      </c>
+      <c r="F80" s="8">
+        <v>149500</v>
+      </c>
+      <c r="G80" s="11">
+        <v>7300</v>
+      </c>
+      <c r="H80" s="11">
+        <f t="shared" si="8"/>
+        <v>520</v>
+      </c>
+      <c r="I80" s="8">
+        <f t="shared" si="9"/>
+        <v>8400</v>
+      </c>
+      <c r="J80" s="8">
+        <f t="shared" si="10"/>
+        <v>1580</v>
+      </c>
+      <c r="K80" s="8">
+        <f t="shared" ref="K80:L80" si="16">K79+5</f>
+        <v>400</v>
+      </c>
+      <c r="L80" s="8">
+        <f t="shared" si="16"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
